--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484712_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484712_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8724</v>
+        <v>2.2942</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4592</v>
+        <v>1.8874</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4132</v>
+        <v>0.4068</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7566</v>
+        <v>-0.3209</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2866</v>
+        <v>0.7615</v>
       </c>
       <c r="I2" t="n">
-        <v>0.47</v>
+        <v>-1.0824</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5166</v>
+        <v>0.4703</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3932</v>
+        <v>1.1199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1234</v>
+        <v>-0.6496</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.76</v>
+        <v>-0.7913</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1066</v>
+        <v>-0.3584</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3466</v>
+        <v>-0.4329</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1322</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1914</v>
+        <v>0.5777</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6599</v>
+        <v>0.5118</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5315</v>
+        <v>0.0659</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9434</v>
+        <v>2.7922</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6415999999999999</v>
+        <v>2.7922</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>M. TAEÑO ELEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2761</v>
+        <v>1.5509</v>
       </c>
       <c r="E3" t="n">
-        <v>1.79</v>
+        <v>1.5509</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4861</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3209</v>
+        <v>1.5509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7615</v>
+        <v>0.317</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0824</v>
+        <v>1.2339</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4703</v>
+        <v>1.5509</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1199</v>
+        <v>0.317</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6496</v>
+        <v>1.2339</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7913</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3584</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4329</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5596</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4144</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1452</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TAEÑO ELEZ</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5509</v>
+        <v>1.2703</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5509</v>
+        <v>1.0951</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.1751</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5509</v>
+        <v>1.7566</v>
       </c>
       <c r="H4" t="n">
-        <v>0.317</v>
+        <v>1.2866</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2339</v>
+        <v>0.47</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5509</v>
+        <v>2.5166</v>
       </c>
       <c r="K4" t="n">
-        <v>0.317</v>
+        <v>2.3932</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2339</v>
+        <v>0.1234</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.1066</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.3466</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.5893</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.2959</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.2934</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4613</v>
+        <v>-0.5058</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6766</v>
+        <v>1.5792</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1379</v>
+        <v>-2.085</v>
       </c>
       <c r="G6" t="n">
         <v>0.1543</v>
@@ -922,13 +922,13 @@
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.472</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5349</v>
+        <v>0.4374</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0069</v>
+        <v>-0.954</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1435</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9526</v>
+        <v>-1.3326</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3305</v>
+        <v>-1.5254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3779</v>
+        <v>0.1927</v>
       </c>
       <c r="G7" t="n">
         <v>3.009</v>
@@ -1000,13 +1000,13 @@
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5161</v>
+        <v>-0.8961</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0617</v>
+        <v>-0.1332</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5778</v>
+        <v>-0.763</v>
       </c>
       <c r="V7" t="n">
         <v>-0.4263</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7475</v>
+        <v>-1.6072</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1379</v>
+        <v>-2.1066</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6096</v>
+        <v>0.4994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4156</v>
+        <v>-0.9266</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3357</v>
+        <v>-1.5762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7514</v>
+        <v>0.6496</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8774999999999999</v>
+        <v>-0.2426</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1698</v>
+        <v>-0.2426</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7077</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4619</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-1.3335</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0437</v>
+        <v>0.6496</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-2.0757</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-3.2079</v>
       </c>
       <c r="R8" t="n">
         <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7047</v>
+        <v>0.2629</v>
       </c>
       <c r="T8" t="n">
-        <v>1.834</v>
+        <v>0.2117</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8707</v>
+        <v>0.0512</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7922</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3002</v>
+        <v>-2.1763</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6872</v>
+        <v>-0.5898</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6129</v>
+        <v>-1.5865</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0726</v>
@@ -1156,13 +1156,13 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1711</v>
+        <v>-0.0472</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5538</v>
+        <v>-2.8793</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7886</v>
+        <v>-2.6204</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2349</v>
+        <v>-0.259</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9266</v>
+        <v>-1.5794</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5762</v>
+        <v>-1.5128</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6496</v>
+        <v>-0.0667</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2426</v>
+        <v>-0.3651</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2426</v>
+        <v>-0.4062</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.2144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3335</v>
+        <v>-1.1066</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6496</v>
+        <v>-0.1078</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.0757</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6837</v>
+        <v>-0.9867</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4703</v>
+        <v>-0.1796</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2134</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2523</v>
+        <v>-3.3749</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.205</v>
+        <v>-2.2097</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0473</v>
+        <v>-1.1651</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5794</v>
+        <v>0.4156</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5128</v>
+        <v>-0.3357</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0667</v>
+        <v>0.7514</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3651</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4062</v>
+        <v>0.1698</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0411</v>
+        <v>0.7077</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2144</v>
+        <v>-0.4619</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1066</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1078</v>
+        <v>0.0437</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0757</v>
+        <v>-3.2079</v>
       </c>
       <c r="R11" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3596</v>
+        <v>1.0774</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7642</v>
+        <v>0.7622</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5954</v>
+        <v>0.3152</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1245</v>
+        <v>-2.7922</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1245</v>
+        <v>-2.1506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4509</v>
+        <v>-4.8066</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9162</v>
+        <v>-3.6661</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5347</v>
+        <v>-1.1405</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1467</v>
+        <v>-3.5659</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2332</v>
+        <v>-1.9463</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.3799</v>
+        <v>-1.6196</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5641</v>
+        <v>-2.3403</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2099</v>
+        <v>-0.4171</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.774</v>
+        <v>-1.9231</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5826</v>
+        <v>-1.2257</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9767</v>
+        <v>-1.5292</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6059</v>
+        <v>0.3035</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>-1.3209</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4315</v>
+        <v>-0.8143</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5349</v>
+        <v>-0.0049</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1034</v>
+        <v>-0.8094</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.547</v>
+        <v>-0.4263</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.547</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1332</v>
+        <v>-4.9289</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.543</v>
+        <v>-3.5265</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5903</v>
+        <v>-1.4024</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5659</v>
+        <v>-4.1467</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9463</v>
+        <v>0.2332</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6196</v>
+        <v>-4.3799</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3403</v>
+        <v>-2.5641</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4171</v>
+        <v>1.2099</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9231</v>
+        <v>-3.774</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2257</v>
+        <v>-1.5826</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5292</v>
+        <v>-0.9767</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3035</v>
+        <v>-0.6059</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3209</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1409</v>
+        <v>0.9535</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8818</v>
+        <v>0.9246</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2591</v>
+        <v>0.0289</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4263</v>
+        <v>-1.547</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4263</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.4966</v>
+        <v>-7.1526</v>
       </c>
       <c r="E14" t="n">
         <v>-5.0382</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4584</v>
+        <v>-2.1145</v>
       </c>
       <c r="G14" t="n">
         <v>1.9724</v>
@@ -1546,13 +1546,13 @@
         <v>1.6983</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0793</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>0.4173</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4966</v>
+        <v>-1.1527</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4643</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-23.332</v>
+        <v>-23.3318</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.8529</v>
+        <v>-14.8531</v>
       </c>
       <c r="F15" t="n">
         <v>-8.479000000000001</v>
@@ -1606,7 +1606,7 @@
         <v>-4.7653</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.872</v>
+        <v>-9.871999999999998</v>
       </c>
       <c r="N15" t="n">
         <v>-11.0658</v>
@@ -1624,16 +1624,16 @@
         <v>14.1525</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4645000000000006</v>
+        <v>0.4644999999999997</v>
       </c>
       <c r="T15" t="n">
-        <v>4.282000000000001</v>
+        <v>4.2818</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.8175</v>
+        <v>-3.8173</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.3205</v>
+        <v>-5.320499999999999</v>
       </c>
       <c r="W15" t="n">
         <v>3.6216</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.4518</v>
+        <v>5.7051</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0345</v>
+        <v>3.7187</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4173</v>
+        <v>1.9864</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1719</v>
+        <v>2.3835</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3999</v>
+        <v>-0.4414</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5718</v>
+        <v>2.8249</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0505</v>
+        <v>2.8837</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8037</v>
+        <v>0.925</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2468</v>
+        <v>1.9587</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8786</v>
+        <v>-0.5001</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2036</v>
+        <v>-1.3664</v>
       </c>
       <c r="O16" t="n">
-        <v>0.325</v>
+        <v>0.8663</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4531</v>
+        <v>4.3401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3966</v>
+        <v>4.3401</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6382</v>
+        <v>-0.0751</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4371</v>
+        <v>0.5332</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2011</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1886</v>
+        <v>-0.9434</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4904</v>
+        <v>0.3018</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.785</v>
+        <v>5.549</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0367</v>
+        <v>3.4755</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7483</v>
+        <v>2.0734</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3835</v>
+        <v>0.1719</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4414</v>
+        <v>-0.3999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8249</v>
+        <v>0.5718</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8837</v>
+        <v>1.0505</v>
       </c>
       <c r="K17" t="n">
-        <v>0.925</v>
+        <v>0.8037</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9587</v>
+        <v>0.2468</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5001</v>
+        <v>-0.8786</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3664</v>
+        <v>-1.2036</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8663</v>
+        <v>0.325</v>
       </c>
       <c r="P17" t="n">
-        <v>4.3401</v>
+        <v>2.4531</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>4.3401</v>
+        <v>3.3966</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9952</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1488</v>
+        <v>0.8782</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8465</v>
+        <v>-0.1428</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9434</v>
+        <v>2.1886</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3018</v>
+        <v>2.4904</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7062</v>
+        <v>5.2199</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0403</v>
+        <v>3.5274</v>
       </c>
       <c r="F18" t="n">
-        <v>1.666</v>
+        <v>1.6924</v>
       </c>
       <c r="G18" t="n">
         <v>2.6992</v>
@@ -1858,13 +1858,13 @@
         <v>3.9627</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0311</v>
+        <v>-0.5175</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5632</v>
+        <v>-0.076</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4679</v>
+        <v>-0.4414</v>
       </c>
       <c r="V18" t="n">
         <v>0.019</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7172</v>
+        <v>3.4521</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3201</v>
+        <v>0.3427</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3971</v>
+        <v>3.1094</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2071</v>
+        <v>0.231</v>
       </c>
       <c r="H19" t="n">
-        <v>0.709</v>
+        <v>0.8335</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4981</v>
+        <v>-0.6024</v>
       </c>
       <c r="J19" t="n">
-        <v>1.49</v>
+        <v>-0.4881</v>
       </c>
       <c r="K19" t="n">
-        <v>1.49</v>
+        <v>0.8507</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.3388</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2829</v>
+        <v>0.7191</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.781</v>
+        <v>-0.0172</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4981</v>
+        <v>0.7363</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6983</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>2.4531</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1516</v>
+        <v>0.1648</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4907</v>
+        <v>0.5674</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3391</v>
+        <v>-0.4026</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3398</v>
+        <v>4.3772</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2828</v>
+        <v>4.0374</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6226</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7242</v>
+        <v>3.0087</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7291</v>
+        <v>1.6381</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4533</v>
+        <v>1.3707</v>
       </c>
       <c r="G20" t="n">
-        <v>0.231</v>
+        <v>1.2071</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8335</v>
+        <v>0.709</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6024</v>
+        <v>0.4981</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4881</v>
+        <v>1.49</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8507</v>
+        <v>1.49</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3388</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7191</v>
+        <v>-0.2829</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0172</v>
+        <v>-0.781</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7363</v>
+        <v>0.4981</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4531</v>
+        <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5631</v>
+        <v>0.4431</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5044</v>
+        <v>0.8087</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0587</v>
+        <v>-0.3656</v>
       </c>
       <c r="V20" t="n">
-        <v>4.3772</v>
+        <v>-0.3398</v>
       </c>
       <c r="W20" t="n">
-        <v>4.0374</v>
+        <v>0.2828</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3398</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5038</v>
+        <v>2.0431</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0152</v>
+        <v>1.528</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4886</v>
+        <v>0.515</v>
       </c>
       <c r="G21" t="n">
         <v>0.369</v>
@@ -2092,13 +2092,13 @@
         <v>2.2644</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1722</v>
+        <v>-0.2885</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4761</v>
+        <v>-0.0111</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3039</v>
+        <v>-0.2774</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3018</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.0789</v>
+        <v>1.6878</v>
       </c>
       <c r="E22" t="n">
-        <v>1.806</v>
+        <v>-1.5955</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2729</v>
+        <v>3.2833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3282</v>
+        <v>-2.8655</v>
       </c>
       <c r="H22" t="n">
-        <v>2.419</v>
+        <v>-1.0487</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-1.8168</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5108</v>
+        <v>-2.6208</v>
       </c>
       <c r="K22" t="n">
-        <v>4.0781</v>
+        <v>-0.7388</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5673</v>
+        <v>-1.882</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1826</v>
+        <v>-0.2447</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6591</v>
+        <v>-0.3099</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4765</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1887</v>
+        <v>2.4531</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6418</v>
+        <v>3.3966</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.2134</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1257</v>
+        <v>0.7236</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5637</v>
+        <v>-0.5102</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6226</v>
+        <v>1.8868</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6226</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8572</v>
+        <v>1.3259</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5226</v>
+        <v>1.0265</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3798</v>
+        <v>0.2994</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9834</v>
+        <v>2.3282</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6544</v>
+        <v>2.419</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.329</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0089</v>
+        <v>3.5108</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.792</v>
+        <v>4.0781</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2169</v>
+        <v>-0.5673</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0254</v>
+        <v>-1.1826</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.6591</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8878</v>
+        <v>0.4765</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2644</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2644</v>
+        <v>2.6418</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2744</v>
+        <v>-0.1911</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1844</v>
+        <v>0.3462</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09</v>
+        <v>-0.5372</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3018</v>
+        <v>-0.6226</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2011</v>
+        <v>1.0081</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7647</v>
+        <v>-1.1072</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9658</v>
+        <v>2.1153</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8655</v>
+        <v>-1.9834</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0487</v>
+        <v>-1.6544</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8168</v>
+        <v>-0.329</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.6208</v>
+        <v>-2.0089</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7388</v>
+        <v>-0.792</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.882</v>
+        <v>-1.2169</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2447</v>
+        <v>0.0254</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3099</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.8878</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4531</v>
+        <v>2.2644</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3966</v>
+        <v>2.2644</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2733</v>
+        <v>0.4253</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4456</v>
+        <v>0.5998</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8277</v>
+        <v>-0.1745</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8868</v>
+        <v>0.3018</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8737</v>
+        <v>-1.5201</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5296</v>
+        <v>-1.3348</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.344</v>
+        <v>-0.1853</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7275</v>
@@ -2404,13 +2404,13 @@
         <v>1.1322</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.283</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2839</v>
+        <v>-0.1252</v>
       </c>
       <c r="V25" t="n">
         <v>0.3018</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. HURYNOWICZ</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.1007</v>
+        <v>-2.0468</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.279</v>
+        <v>-1.8388</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8217</v>
+        <v>-0.208</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0959</v>
+        <v>-0.4729</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1847</v>
+        <v>-2.1678</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0888</v>
+        <v>1.6949</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2281</v>
+        <v>1.0336</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3803</v>
+        <v>-0.8343</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6084000000000001</v>
+        <v>1.8679</v>
       </c>
       <c r="M26" t="n">
-        <v>0.324</v>
+        <v>-1.5066</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1956</v>
+        <v>-1.3335</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5196</v>
+        <v>-0.173</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1887</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8383</v>
+        <v>-0.2529</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3527</v>
+        <v>-0.0419</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4855</v>
+        <v>-0.211</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>P. HURYNOWICZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7191</v>
+        <v>-2.1007</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.326</v>
+        <v>-0.279</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3932</v>
+        <v>-1.8217</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4729</v>
+        <v>0.0959</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.1678</v>
+        <v>0.1847</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6949</v>
+        <v>-0.0888</v>
       </c>
       <c r="J27" t="n">
-        <v>1.0336</v>
+        <v>-0.2281</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.8343</v>
+        <v>0.3803</v>
       </c>
       <c r="L27" t="n">
-        <v>1.8679</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.5066</v>
+        <v>0.324</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.3335</v>
+        <v>-0.1956</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.173</v>
+        <v>0.5196</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.9253</v>
+        <v>-0.8383</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5291</v>
+        <v>-0.3527</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3962</v>
+        <v>-0.4855</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>23.3319</v>
+        <v>23.3321</v>
       </c>
       <c r="E28" t="n">
-        <v>9.101800000000001</v>
+        <v>9.101600000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>14.2302</v>
+        <v>14.2303</v>
       </c>
       <c r="G28" t="n">
         <v>2.4365</v>
@@ -2608,10 +2608,10 @@
         <v>-1.1348</v>
       </c>
       <c r="I28" t="n">
-        <v>3.571200000000001</v>
+        <v>3.5712</v>
       </c>
       <c r="J28" t="n">
-        <v>9.871800000000002</v>
+        <v>9.8718</v>
       </c>
       <c r="K28" t="n">
         <v>11.0657</v>
@@ -2638,16 +2638,16 @@
         <v>30.192</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.4645000000000006</v>
+        <v>-0.4643999999999998</v>
       </c>
       <c r="T28" t="n">
         <v>3.8175</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.282</v>
+        <v>-4.2818</v>
       </c>
       <c r="V28" t="n">
-        <v>5.320600000000001</v>
+        <v>5.320600000000002</v>
       </c>
       <c r="W28" t="n">
         <v>9.5648</v>
